--- a/outputs/analysis_results/01_short-horizon portfolio performance/01_portfolio_weekly_h1_cn.xlsx
+++ b/outputs/analysis_results/01_short-horizon portfolio performance/01_portfolio_weekly_h1_cn.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weekly R5 portfolio summary from step-04 CNN all_h1.xlsx and step-05 benchmark h1.xlsx.</t>
+          <t>Weekly R5 portfolio summary from step-04 CNN all_h{k}.xlsx and step-05 benchmark h{k}.xlsx.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Turnover row: Turnover (annualized) on H-L (DH) portfolio.</t>
+          <t>H-L: eval horizon H1 (signal at t, return over 1st future rebalance period).</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H-L return stars use Newey-West t-stat on the long-short spread.</t>
+          <t>DH Ret2 / DH Ret3: H-L (DH) annualized return at eval horizons H2 / H3 (2nd / 3rd future rebalance period).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Turnover row: monthly turnover on H-L (DH), paper Table I / GKX (2020) convention (R5 one-week holding ≈ 0.25 month; scaled from backtest Turnover (annualized)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H-L and DH Ret2/Ret3 return stars use Newey-West t-stat on the long-short spread.</t>
         </is>
       </c>
     </row>
@@ -551,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1546,48 +1570,48 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>DH Ret2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>0.09 (1.35)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>0.12* (1.82)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>0.07 (1.35)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-0.01 (-0.16)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>0.41*** (3.68)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>89%</t>
+          <t>0.16* (1.94)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>0.05 (0.78)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -1595,166 +1619,110 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FloatCap-Weight</t>
+          <t>Equal-Weight</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>DH Ret3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
+          <t>0.08 (1.29)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
+          <t>0.07 (1.19)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.04 (0.80)</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
+          <t>0.02 (0.22)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-0.14</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
+          <t>0.34*** (3.33)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>-0.38</t>
-        </is>
-      </c>
+          <t>0.13* (1.75)</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-0.11</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>-0.33</t>
-        </is>
-      </c>
+          <t>-0.04 (-0.72)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FloatCap-Weight</t>
+          <t>Equal-Weight</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>-0.00</t>
-        </is>
-      </c>
+          <t>656%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
+          <t>650%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
+          <t>659%</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
+          <t>135%</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
+          <t>373%</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
+          <t>683%</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
+          <t>477%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1764,77 +1732,77 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>-0.27</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.33</t>
         </is>
       </c>
     </row>
@@ -1846,77 +1814,77 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>-0.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.28</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
@@ -1928,77 +1896,77 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>0.33</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.07</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
@@ -2010,77 +1978,77 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.32</t>
         </is>
       </c>
     </row>
@@ -2092,77 +2060,77 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>0.31</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.40</t>
         </is>
       </c>
     </row>
@@ -2174,77 +2142,77 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0.50</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
@@ -2256,7 +2224,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2271,62 +2239,62 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>0.19</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.43</t>
         </is>
       </c>
     </row>
@@ -2338,77 +2306,77 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
           <t>0.49</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>0.39</t>
         </is>
       </c>
     </row>
@@ -2420,77 +2388,77 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H-L</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.23** (2.47)</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.22** (2.46)</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.16* (1.90)</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.03 (0.24)</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>0.12</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.33*** (2.61)</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>0.21* (1.94)</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.24** (2.11)</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>0.54</t>
         </is>
       </c>
     </row>
@@ -2502,379 +2470,323 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>0.19</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>H-L</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>0.23** (2.47)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.22** (2.46)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.16* (1.90)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03 (0.24)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.33*** (2.61)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.21* (1.94)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.24** (2.11)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.12</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DH Ret2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
+          <t>0.04 (0.72)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0.12</t>
-        </is>
-      </c>
+          <t>0.04 (0.63)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
+          <t>0.03 (0.47)</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>0.19</t>
-        </is>
-      </c>
+          <t>0.05 (0.49)</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
+          <t>0.33** (2.24)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
+          <t>0.06 (0.53)</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
+          <t>0.03 (0.38)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>DH Ret3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
+          <t>0.09 (1.24)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
+          <t>0.10 (1.48)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
+          <t>0.09 (1.40)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>0.14</t>
-        </is>
-      </c>
+          <t>0.11 (1.10)</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
+          <t>0.35** (2.49)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>0.12</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>0.41</t>
-        </is>
-      </c>
+          <t>-0.03 (-0.28)</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
+          <t>-0.03 (-0.32)</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
+          <t>676%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
+          <t>672%</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
+          <t>682%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
+          <t>149%</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
+          <t>406%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
+          <t>701%</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
+          <t>512%</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2884,77 +2796,77 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.10</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>-0.33</t>
         </is>
       </c>
     </row>
@@ -2966,77 +2878,77 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.00</t>
         </is>
       </c>
     </row>
@@ -3048,77 +2960,77 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
           <t>0.15</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>0.20</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>0.10</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>0.32</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>0.44</t>
         </is>
       </c>
     </row>
@@ -3130,77 +3042,77 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.30</t>
         </is>
       </c>
     </row>
@@ -3212,77 +3124,77 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>0.30</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.21</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>0.46</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>0.11</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>0.36</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>0.22</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>0.17</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.40</t>
         </is>
       </c>
     </row>
@@ -3294,77 +3206,77 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
           <t>0.48</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>0.09</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>0.24</t>
-        </is>
-      </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
     </row>
@@ -3376,77 +3288,77 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H-L</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.23** (2.47)</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.22** (2.50)</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.16** (1.98)</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.03 (0.22)</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.32** (2.57)</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.20* (1.87)</t>
+          <t>0.10</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>0.24** (2.10)</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.44</t>
         </is>
       </c>
     </row>
@@ -3458,51 +3370,487 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0.43</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0.12</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0.29</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.36</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>0.20</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0.09</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0.24</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0.13</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H-L</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0.23** (2.47)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>0.22** (2.50)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.16** (1.98)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0.03 (0.22)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0.32** (2.57)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>0.20* (1.87)</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0.24** (2.10)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DH Ret2</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.05 (0.86)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>0.04 (0.71)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.03 (0.55)</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0.05 (0.46)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>0.33** (2.24)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>0.05 (0.52)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0.03 (0.39)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DH Ret3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0.10 (1.30)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>0.11 (1.51)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.09 (1.43)</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0.11 (1.05)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0.34** (2.44)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>-0.03 (-0.29)</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>-0.03 (-0.32)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>19%</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>678%</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>672%</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>684%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>150%</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>408%</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>701%</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>514%</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3515,7 +3863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3936,95 +4284,95 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>DH Ret2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>85.33</v>
+        <v>0.0948</v>
       </c>
       <c r="D13" t="n">
-        <v>84.52</v>
+        <v>0.1223</v>
       </c>
       <c r="E13" t="n">
-        <v>85.73</v>
+        <v>0.0742</v>
       </c>
       <c r="F13" t="n">
-        <v>17.52</v>
+        <v>-0.0115</v>
       </c>
       <c r="G13" t="n">
-        <v>48.46</v>
+        <v>0.4063</v>
       </c>
       <c r="H13" t="n">
-        <v>88.77</v>
+        <v>0.1608</v>
       </c>
       <c r="I13" t="n">
-        <v>62.02</v>
+        <v>0.0546</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FloatCap-Weight</t>
+          <t>Equal-Weight</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>DH Ret3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.0565</v>
+        <v>0.0786</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0127</v>
+        <v>0.0674</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0114</v>
+        <v>0.0372</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0558</v>
+        <v>0.0161</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1407</v>
+        <v>0.3431</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.115</v>
+        <v>0.1275</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1097</v>
+        <v>-0.044</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FloatCap-Weight</t>
+          <t>Equal-Weight</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.0013</v>
+        <v>656.3846153846154</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0373</v>
+        <v>650.1538461538461</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.005</v>
+        <v>659.4615384615385</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0584</v>
+        <v>134.7692307692308</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0349</v>
+        <v>372.7692307692308</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0568</v>
+        <v>682.8461538461538</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0058</v>
+        <v>477.0769230769231</v>
       </c>
     </row>
     <row r="16">
@@ -4035,29 +4383,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.0172</v>
+        <v>-0.0565</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1046</v>
+        <v>-0.0127</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0824</v>
+        <v>0.0114</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0477</v>
+        <v>0.0558</v>
       </c>
       <c r="G16" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.1407</v>
       </c>
       <c r="H16" t="n">
-        <v>0.119</v>
+        <v>-0.115</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0464</v>
+        <v>-0.1097</v>
       </c>
     </row>
     <row r="17">
@@ -4068,29 +4416,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.0013</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0312</v>
+        <v>0.0373</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.005</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0434</v>
+        <v>0.0584</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1483</v>
+        <v>0.0349</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1025</v>
+        <v>0.0568</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0979</v>
+        <v>0.0058</v>
       </c>
     </row>
     <row r="18">
@@ -4101,29 +4449,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.1023</v>
+        <v>0.0172</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0713</v>
+        <v>0.1046</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0824</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0682</v>
+        <v>0.0477</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1408</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1367</v>
+        <v>0.119</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1152</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="19">
@@ -4134,29 +4482,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.115</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0522</v>
+        <v>0.0312</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0711</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0699</v>
+        <v>0.0434</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1818</v>
+        <v>0.1483</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1584</v>
+        <v>0.1025</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1098</v>
+        <v>0.0979</v>
       </c>
     </row>
     <row r="20">
@@ -4167,29 +4515,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1551</v>
+        <v>0.1023</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0956</v>
+        <v>0.0713</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1077</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0509</v>
+        <v>0.0682</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1939</v>
+        <v>0.1408</v>
       </c>
       <c r="H20" t="n">
-        <v>0.115</v>
+        <v>0.1367</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1278</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="21">
@@ -4200,29 +4548,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.1394</v>
+        <v>0.115</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1378</v>
+        <v>0.0522</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1052</v>
+        <v>0.0711</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1169</v>
+        <v>0.0699</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1794</v>
+        <v>0.1818</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1514</v>
+        <v>0.1584</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1505</v>
+        <v>0.1098</v>
       </c>
     </row>
     <row r="22">
@@ -4233,29 +4581,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.1575</v>
+        <v>0.1551</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1883</v>
+        <v>0.0956</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0927</v>
+        <v>0.1077</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1187</v>
+        <v>0.0509</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2191</v>
+        <v>0.1939</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1249</v>
+        <v>0.115</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1707</v>
+        <v>0.1278</v>
       </c>
     </row>
     <row r="23">
@@ -4266,29 +4614,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1711</v>
+        <v>0.1394</v>
       </c>
       <c r="D23" t="n">
-        <v>0.2036</v>
+        <v>0.1378</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1667</v>
+        <v>0.1052</v>
       </c>
       <c r="F23" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.1169</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1872</v>
+        <v>0.1794</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1514</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1337</v>
+        <v>0.1505</v>
       </c>
     </row>
     <row r="24">
@@ -4299,29 +4647,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H-L</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.2276</v>
+        <v>0.1575</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2163</v>
+        <v>0.1883</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1553</v>
+        <v>0.0927</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0272</v>
+        <v>0.1187</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3279</v>
+        <v>0.2191</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2094</v>
+        <v>0.1249</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2435</v>
+        <v>0.1707</v>
       </c>
     </row>
     <row r="25">
@@ -4332,161 +4680,161 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Turnover</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>87.94</v>
+        <v>0.1711</v>
       </c>
       <c r="D25" t="n">
-        <v>87.31</v>
+        <v>0.2036</v>
       </c>
       <c r="E25" t="n">
-        <v>88.70999999999999</v>
+        <v>0.1667</v>
       </c>
       <c r="F25" t="n">
-        <v>19.34</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>52.81</v>
+        <v>0.1872</v>
       </c>
       <c r="H25" t="n">
-        <v>91.06999999999999</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>66.56</v>
+        <v>0.1337</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>H-L</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-0.0582</v>
+        <v>0.2276</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.0177</v>
+        <v>0.2163</v>
       </c>
       <c r="E26" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.1553</v>
       </c>
       <c r="F26" t="n">
-        <v>0.053</v>
+        <v>0.0272</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1404</v>
+        <v>0.3279</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1135</v>
+        <v>0.2094</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1103</v>
+        <v>0.2435</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DH Ret2</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.0036</v>
+        <v>0.0436</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0365</v>
+        <v>0.0364</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0116</v>
+        <v>0.0266</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0562</v>
+        <v>0.0512</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0366</v>
+        <v>0.3279</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0604</v>
+        <v>0.0555</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0004</v>
+        <v>0.0305</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>DH Ret3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.0168</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1062</v>
+        <v>0.101</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0837</v>
+        <v>0.0864</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0415</v>
+        <v>0.113</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.3458</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1216</v>
+        <v>-0.0261</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0451</v>
+        <v>-0.0288</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Turnover</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.09320000000000001</v>
+        <v>676.4615384615385</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0281</v>
+        <v>671.6153846153846</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0839</v>
+        <v>682.3846153846154</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0391</v>
+        <v>148.7692307692308</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1471</v>
+        <v>406.2307692307693</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1019</v>
+        <v>700.5384615384614</v>
       </c>
       <c r="I29" t="n">
-        <v>0.091</v>
+        <v>512</v>
       </c>
     </row>
     <row r="30">
@@ -4497,29 +4845,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.1056</v>
+        <v>-0.0582</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0746</v>
+        <v>-0.0177</v>
       </c>
       <c r="E30" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0626</v>
+        <v>0.053</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1415</v>
+        <v>-0.1404</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1344</v>
+        <v>-0.1135</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1135</v>
+        <v>-0.1103</v>
       </c>
     </row>
     <row r="31">
@@ -4530,29 +4878,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.1109</v>
+        <v>0.0036</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0494</v>
+        <v>0.0365</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0668</v>
+        <v>-0.0116</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0689</v>
+        <v>0.0562</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1856</v>
+        <v>0.0366</v>
       </c>
       <c r="H31" t="n">
-        <v>0.1529</v>
+        <v>0.0604</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1096</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="32">
@@ -4563,29 +4911,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1514</v>
+        <v>0.0168</v>
       </c>
       <c r="D32" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.1062</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1045</v>
+        <v>0.0837</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0484</v>
+        <v>0.0415</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1957</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>0.1038</v>
+        <v>0.1216</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1304</v>
+        <v>0.0451</v>
       </c>
     </row>
     <row r="33">
@@ -4596,29 +4944,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.137</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1352</v>
+        <v>0.0281</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1104</v>
+        <v>0.0839</v>
       </c>
       <c r="F33" t="n">
-        <v>0.1221</v>
+        <v>0.0391</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1775</v>
+        <v>0.1471</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1509</v>
+        <v>0.1019</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1466</v>
+        <v>0.091</v>
       </c>
     </row>
     <row r="34">
@@ -4629,29 +4977,29 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1514</v>
+        <v>0.1056</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1842</v>
+        <v>0.0746</v>
       </c>
       <c r="E34" t="n">
-        <v>0.0901</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.1143</v>
+        <v>0.0626</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2208</v>
+        <v>0.1415</v>
       </c>
       <c r="H34" t="n">
-        <v>0.1265</v>
+        <v>0.1344</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1694</v>
+        <v>0.1135</v>
       </c>
     </row>
     <row r="35">
@@ -4662,29 +5010,29 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.1675</v>
+        <v>0.1109</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1997</v>
+        <v>0.0494</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1673</v>
+        <v>0.0668</v>
       </c>
       <c r="F35" t="n">
-        <v>0.078</v>
+        <v>0.0689</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1844</v>
+        <v>0.1856</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0888</v>
+        <v>0.1529</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1345</v>
+        <v>0.1096</v>
       </c>
     </row>
     <row r="36">
@@ -4695,29 +5043,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>H-L</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.2257</v>
+        <v>0.1514</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2174</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1579</v>
+        <v>0.1045</v>
       </c>
       <c r="F36" t="n">
-        <v>0.025</v>
+        <v>0.0484</v>
       </c>
       <c r="G36" t="n">
-        <v>0.3248</v>
+        <v>0.1957</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2024</v>
+        <v>0.1038</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2447</v>
+        <v>0.1304</v>
       </c>
     </row>
     <row r="37">
@@ -4728,29 +5076,227 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.1352</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.1104</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1775</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1509</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.1466</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0901</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.1265</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.1694</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.1675</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.1673</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.0888</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.1345</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>H-L</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.1579</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2024</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.2447</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>DH Ret2</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>0.0514</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.0401</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.0321</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>DH Ret3</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.1062</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.1093</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-0.0279</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-0.0288</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>Turnover</t>
         </is>
       </c>
-      <c r="C37" t="n">
-        <v>88.12</v>
-      </c>
-      <c r="D37" t="n">
-        <v>87.42</v>
-      </c>
-      <c r="E37" t="n">
-        <v>88.88</v>
-      </c>
-      <c r="F37" t="n">
-        <v>19.46</v>
-      </c>
-      <c r="G37" t="n">
-        <v>52.98</v>
-      </c>
-      <c r="H37" t="n">
-        <v>91.14</v>
-      </c>
-      <c r="I37" t="n">
-        <v>66.84999999999999</v>
+      <c r="C43" t="n">
+        <v>677.8461538461538</v>
+      </c>
+      <c r="D43" t="n">
+        <v>672.4615384615385</v>
+      </c>
+      <c r="E43" t="n">
+        <v>683.6923076923076</v>
+      </c>
+      <c r="F43" t="n">
+        <v>149.6923076923077</v>
+      </c>
+      <c r="G43" t="n">
+        <v>407.5384615384615</v>
+      </c>
+      <c r="H43" t="n">
+        <v>701.0769230769231</v>
+      </c>
+      <c r="I43" t="n">
+        <v>514.2307692307692</v>
       </c>
     </row>
   </sheetData>
@@ -4764,7 +5310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5180,67 +5726,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FloatCap-Weight</t>
+          <t>Equal-Weight</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>DH Ret2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.265</v>
+        <v>0.59</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.055</v>
+        <v>0.788</v>
       </c>
       <c r="E13" t="n">
-        <v>0.047</v>
+        <v>0.551</v>
       </c>
       <c r="F13" t="n">
-        <v>0.176</v>
+        <v>-0.067</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.448</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.38</v>
+        <v>0.925</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.331</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FloatCap-Weight</t>
+          <t>Equal-Weight</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DH Ret3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.004</v>
+        <v>0.653</v>
       </c>
       <c r="D14" t="n">
-        <v>0.127</v>
+        <v>0.609</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.017</v>
+        <v>0.379</v>
       </c>
       <c r="F14" t="n">
-        <v>0.194</v>
+        <v>0.095</v>
       </c>
       <c r="G14" t="n">
-        <v>0.125</v>
+        <v>1.993</v>
       </c>
       <c r="H14" t="n">
-        <v>0.191</v>
+        <v>0.782</v>
       </c>
       <c r="I14" t="n">
-        <v>0.019</v>
+        <v>-0.336</v>
       </c>
     </row>
     <row r="15">
@@ -5251,29 +5797,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.054</v>
+        <v>-0.265</v>
       </c>
       <c r="D15" t="n">
-        <v>0.329</v>
+        <v>-0.055</v>
       </c>
       <c r="E15" t="n">
-        <v>0.268</v>
+        <v>0.047</v>
       </c>
       <c r="F15" t="n">
-        <v>0.161</v>
+        <v>0.176</v>
       </c>
       <c r="G15" t="n">
-        <v>0.324</v>
+        <v>-0.448</v>
       </c>
       <c r="H15" t="n">
-        <v>0.399</v>
+        <v>-0.38</v>
       </c>
       <c r="I15" t="n">
-        <v>0.15</v>
+        <v>-0.331</v>
       </c>
     </row>
     <row r="16">
@@ -5284,29 +5830,29 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.287</v>
+        <v>-0.004</v>
       </c>
       <c r="D16" t="n">
-        <v>0.101</v>
+        <v>0.127</v>
       </c>
       <c r="E16" t="n">
-        <v>0.282</v>
+        <v>-0.017</v>
       </c>
       <c r="F16" t="n">
-        <v>0.144</v>
+        <v>0.194</v>
       </c>
       <c r="G16" t="n">
-        <v>0.478</v>
+        <v>0.125</v>
       </c>
       <c r="H16" t="n">
-        <v>0.333</v>
+        <v>0.191</v>
       </c>
       <c r="I16" t="n">
-        <v>0.317</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="17">
@@ -5317,29 +5863,29 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.326</v>
+        <v>0.054</v>
       </c>
       <c r="D17" t="n">
-        <v>0.229</v>
+        <v>0.329</v>
       </c>
       <c r="E17" t="n">
-        <v>0.308</v>
+        <v>0.268</v>
       </c>
       <c r="F17" t="n">
-        <v>0.226</v>
+        <v>0.161</v>
       </c>
       <c r="G17" t="n">
-        <v>0.458</v>
+        <v>0.324</v>
       </c>
       <c r="H17" t="n">
-        <v>0.432</v>
+        <v>0.399</v>
       </c>
       <c r="I17" t="n">
-        <v>0.402</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="18">
@@ -5350,29 +5896,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.361</v>
+        <v>0.287</v>
       </c>
       <c r="D18" t="n">
-        <v>0.164</v>
+        <v>0.101</v>
       </c>
       <c r="E18" t="n">
-        <v>0.235</v>
+        <v>0.282</v>
       </c>
       <c r="F18" t="n">
-        <v>0.221</v>
+        <v>0.144</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.478</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="I18" t="n">
-        <v>0.37</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="19">
@@ -5383,29 +5929,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.485</v>
+        <v>0.326</v>
       </c>
       <c r="D19" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.308</v>
       </c>
-      <c r="E19" t="n">
-        <v>0.345</v>
-      </c>
       <c r="F19" t="n">
-        <v>0.165</v>
+        <v>0.226</v>
       </c>
       <c r="G19" t="n">
-        <v>0.606</v>
+        <v>0.458</v>
       </c>
       <c r="H19" t="n">
-        <v>0.351</v>
+        <v>0.432</v>
       </c>
       <c r="I19" t="n">
-        <v>0.427</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="20">
@@ -5416,29 +5962,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.439</v>
+        <v>0.361</v>
       </c>
       <c r="D20" t="n">
-        <v>0.437</v>
+        <v>0.164</v>
       </c>
       <c r="E20" t="n">
-        <v>0.332</v>
+        <v>0.235</v>
       </c>
       <c r="F20" t="n">
-        <v>0.38</v>
+        <v>0.221</v>
       </c>
       <c r="G20" t="n">
-        <v>0.531</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.457</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.491</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="21">
@@ -5449,29 +5995,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.479</v>
+        <v>0.485</v>
       </c>
       <c r="D21" t="n">
-        <v>0.582</v>
+        <v>0.308</v>
       </c>
       <c r="E21" t="n">
-        <v>0.297</v>
+        <v>0.345</v>
       </c>
       <c r="F21" t="n">
-        <v>0.376</v>
+        <v>0.165</v>
       </c>
       <c r="G21" t="n">
-        <v>0.633</v>
+        <v>0.606</v>
       </c>
       <c r="H21" t="n">
-        <v>0.362</v>
+        <v>0.351</v>
       </c>
       <c r="I21" t="n">
-        <v>0.537</v>
+        <v>0.427</v>
       </c>
     </row>
     <row r="22">
@@ -5482,29 +6028,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.544</v>
+        <v>0.439</v>
       </c>
       <c r="D22" t="n">
-        <v>0.636</v>
+        <v>0.437</v>
       </c>
       <c r="E22" t="n">
-        <v>0.52</v>
+        <v>0.332</v>
       </c>
       <c r="F22" t="n">
-        <v>0.248</v>
+        <v>0.38</v>
       </c>
       <c r="G22" t="n">
-        <v>0.487</v>
+        <v>0.531</v>
       </c>
       <c r="H22" t="n">
-        <v>0.254</v>
+        <v>0.457</v>
       </c>
       <c r="I22" t="n">
-        <v>0.385</v>
+        <v>0.491</v>
       </c>
     </row>
     <row r="23">
@@ -5515,161 +6061,161 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H-L</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.198</v>
+        <v>0.479</v>
       </c>
       <c r="D23" t="n">
-        <v>1.228</v>
+        <v>0.582</v>
       </c>
       <c r="E23" t="n">
-        <v>0.977</v>
+        <v>0.297</v>
       </c>
       <c r="F23" t="n">
-        <v>0.119</v>
+        <v>0.376</v>
       </c>
       <c r="G23" t="n">
-        <v>1.189</v>
+        <v>0.633</v>
       </c>
       <c r="H23" t="n">
-        <v>0.759</v>
+        <v>0.362</v>
       </c>
       <c r="I23" t="n">
-        <v>1.123</v>
+        <v>0.537</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-0.274</v>
+        <v>0.544</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.076</v>
+        <v>0.636</v>
       </c>
       <c r="E24" t="n">
-        <v>0.039</v>
+        <v>0.52</v>
       </c>
       <c r="F24" t="n">
-        <v>0.168</v>
+        <v>0.248</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.447</v>
+        <v>0.487</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.375</v>
+        <v>0.254</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.334</v>
+        <v>0.385</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>H-L</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.012</v>
+        <v>1.198</v>
       </c>
       <c r="D25" t="n">
-        <v>0.125</v>
+        <v>1.228</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.04</v>
+        <v>0.977</v>
       </c>
       <c r="F25" t="n">
-        <v>0.187</v>
+        <v>0.119</v>
       </c>
       <c r="G25" t="n">
-        <v>0.13</v>
+        <v>1.189</v>
       </c>
       <c r="H25" t="n">
-        <v>0.203</v>
+        <v>0.759</v>
       </c>
       <c r="I25" t="n">
-        <v>0.001</v>
+        <v>1.123</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>DH Ret2</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.052</v>
+        <v>0.27</v>
       </c>
       <c r="D26" t="n">
-        <v>0.336</v>
+        <v>0.23</v>
       </c>
       <c r="E26" t="n">
-        <v>0.274</v>
+        <v>0.188</v>
       </c>
       <c r="F26" t="n">
-        <v>0.14</v>
+        <v>0.228</v>
       </c>
       <c r="G26" t="n">
-        <v>0.318</v>
+        <v>1.369</v>
       </c>
       <c r="H26" t="n">
-        <v>0.411</v>
+        <v>0.257</v>
       </c>
       <c r="I26" t="n">
-        <v>0.147</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TotalCap-Weight</t>
+          <t>FloatCap-Weight</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>DH Ret3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.287</v>
+        <v>0.673</v>
       </c>
       <c r="D27" t="n">
-        <v>0.091</v>
+        <v>0.734</v>
       </c>
       <c r="E27" t="n">
-        <v>0.273</v>
+        <v>0.718</v>
       </c>
       <c r="F27" t="n">
-        <v>0.13</v>
+        <v>0.509</v>
       </c>
       <c r="G27" t="n">
-        <v>0.476</v>
+        <v>1.539</v>
       </c>
       <c r="H27" t="n">
-        <v>0.333</v>
+        <v>-0.119</v>
       </c>
       <c r="I27" t="n">
-        <v>0.297</v>
+        <v>-0.151</v>
       </c>
     </row>
     <row r="28">
@@ -5680,29 +6226,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.34</v>
+        <v>-0.274</v>
       </c>
       <c r="D28" t="n">
-        <v>0.241</v>
+        <v>-0.076</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3</v>
+        <v>0.039</v>
       </c>
       <c r="F28" t="n">
-        <v>0.209</v>
+        <v>0.168</v>
       </c>
       <c r="G28" t="n">
-        <v>0.463</v>
+        <v>-0.447</v>
       </c>
       <c r="H28" t="n">
-        <v>0.428</v>
+        <v>-0.375</v>
       </c>
       <c r="I28" t="n">
-        <v>0.398</v>
+        <v>-0.334</v>
       </c>
     </row>
     <row r="29">
@@ -5713,29 +6259,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.351</v>
+        <v>0.012</v>
       </c>
       <c r="D29" t="n">
-        <v>0.157</v>
+        <v>0.125</v>
       </c>
       <c r="E29" t="n">
-        <v>0.223</v>
+        <v>-0.04</v>
       </c>
       <c r="F29" t="n">
-        <v>0.219</v>
+        <v>0.187</v>
       </c>
       <c r="G29" t="n">
-        <v>0.581</v>
+        <v>0.13</v>
       </c>
       <c r="H29" t="n">
-        <v>0.485</v>
+        <v>0.203</v>
       </c>
       <c r="I29" t="n">
-        <v>0.372</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="30">
@@ -5746,29 +6292,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.475</v>
+        <v>0.052</v>
       </c>
       <c r="D30" t="n">
-        <v>0.316</v>
+        <v>0.336</v>
       </c>
       <c r="E30" t="n">
-        <v>0.338</v>
+        <v>0.274</v>
       </c>
       <c r="F30" t="n">
-        <v>0.158</v>
+        <v>0.14</v>
       </c>
       <c r="G30" t="n">
-        <v>0.616</v>
+        <v>0.318</v>
       </c>
       <c r="H30" t="n">
-        <v>0.318</v>
+        <v>0.411</v>
       </c>
       <c r="I30" t="n">
-        <v>0.439</v>
+        <v>0.147</v>
       </c>
     </row>
     <row r="31">
@@ -5779,29 +6325,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.435</v>
+        <v>0.287</v>
       </c>
       <c r="D31" t="n">
-        <v>0.432</v>
+        <v>0.091</v>
       </c>
       <c r="E31" t="n">
-        <v>0.351</v>
+        <v>0.273</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4</v>
+        <v>0.13</v>
       </c>
       <c r="G31" t="n">
-        <v>0.528</v>
+        <v>0.476</v>
       </c>
       <c r="H31" t="n">
-        <v>0.458</v>
+        <v>0.333</v>
       </c>
       <c r="I31" t="n">
-        <v>0.481</v>
+        <v>0.297</v>
       </c>
     </row>
     <row r="32">
@@ -5812,29 +6358,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C32" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="G32" t="n">
         <v>0.463</v>
       </c>
-      <c r="D32" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.291</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.639</v>
-      </c>
       <c r="H32" t="n">
-        <v>0.369</v>
+        <v>0.428</v>
       </c>
       <c r="I32" t="n">
-        <v>0.535</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="33">
@@ -5845,29 +6391,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.534</v>
+        <v>0.351</v>
       </c>
       <c r="D33" t="n">
-        <v>0.627</v>
+        <v>0.157</v>
       </c>
       <c r="E33" t="n">
-        <v>0.524</v>
+        <v>0.223</v>
       </c>
       <c r="F33" t="n">
-        <v>0.234</v>
+        <v>0.219</v>
       </c>
       <c r="G33" t="n">
-        <v>0.482</v>
+        <v>0.581</v>
       </c>
       <c r="H33" t="n">
-        <v>0.239</v>
+        <v>0.485</v>
       </c>
       <c r="I33" t="n">
-        <v>0.388</v>
+        <v>0.372</v>
       </c>
     </row>
     <row r="34">
@@ -5878,29 +6424,227 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.439</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.481</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.535</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.388</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>H-L</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C38" t="n">
         <v>1.183</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D38" t="n">
         <v>1.229</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E38" t="n">
         <v>0.992</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F38" t="n">
         <v>0.108</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G38" t="n">
         <v>1.169</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H38" t="n">
         <v>0.727</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I38" t="n">
         <v>1.113</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>DH Ret2</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.376</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.166</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TotalCap-Weight</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>DH Ret3</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0.709</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="G40" t="n">
+        <v>1.507</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-0.126</v>
+      </c>
+      <c r="I40" t="n">
+        <v>-0.149</v>
       </c>
     </row>
   </sheetData>
@@ -5976,25 +6720,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85.33</v>
+        <v>656.3846153846154</v>
       </c>
       <c r="D2" t="n">
-        <v>84.52</v>
+        <v>650.1538461538461</v>
       </c>
       <c r="E2" t="n">
-        <v>85.73</v>
+        <v>659.4615384615385</v>
       </c>
       <c r="F2" t="n">
-        <v>17.52</v>
+        <v>134.7692307692308</v>
       </c>
       <c r="G2" t="n">
-        <v>48.46</v>
+        <v>372.7692307692308</v>
       </c>
       <c r="H2" t="n">
-        <v>88.77</v>
+        <v>682.8461538461538</v>
       </c>
       <c r="I2" t="n">
-        <v>62.02</v>
+        <v>477.0769230769231</v>
       </c>
     </row>
     <row r="3">
@@ -6009,25 +6753,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>87.94</v>
+        <v>676.4615384615385</v>
       </c>
       <c r="D3" t="n">
-        <v>87.31</v>
+        <v>671.6153846153846</v>
       </c>
       <c r="E3" t="n">
-        <v>88.70999999999999</v>
+        <v>682.3846153846154</v>
       </c>
       <c r="F3" t="n">
-        <v>19.34</v>
+        <v>148.7692307692308</v>
       </c>
       <c r="G3" t="n">
-        <v>52.81</v>
+        <v>406.2307692307693</v>
       </c>
       <c r="H3" t="n">
-        <v>91.06999999999999</v>
+        <v>700.5384615384614</v>
       </c>
       <c r="I3" t="n">
-        <v>66.56</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4">
@@ -6042,25 +6786,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.12</v>
+        <v>677.8461538461538</v>
       </c>
       <c r="D4" t="n">
-        <v>87.42</v>
+        <v>672.4615384615385</v>
       </c>
       <c r="E4" t="n">
-        <v>88.88</v>
+        <v>683.6923076923076</v>
       </c>
       <c r="F4" t="n">
-        <v>19.46</v>
+        <v>149.6923076923077</v>
       </c>
       <c r="G4" t="n">
-        <v>52.98</v>
+        <v>407.5384615384615</v>
       </c>
       <c r="H4" t="n">
-        <v>91.14</v>
+        <v>701.0769230769231</v>
       </c>
       <c r="I4" t="n">
-        <v>66.84999999999999</v>
+        <v>514.2307692307692</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/analysis_results/01_short-horizon portfolio performance/01_portfolio_weekly_h1_cn.xlsx
+++ b/outputs/analysis_results/01_short-horizon portfolio performance/01_portfolio_weekly_h1_cn.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,60 +447,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>panel: Equal-Weight</t>
+          <t>frequency</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>source sheet='equal'; Equal-weight (EW): 1/N within each decile portfolio.</t>
+          <t>weekly</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>panel: FloatCap-Weight</t>
+          <t>holding_horizon</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>source sheet='float'; Float market-cap weight at formation (CN: FloatCap / 流通市值).</t>
+          <t>R5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>panel: TotalCap-Weight</t>
+          <t>panel: Equal-Weight</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>source sheet='total'; Total market-cap weight at formation (CN: TotalCap / 总市值).</t>
+          <t>source sheet='equal'; Equal-weight (EW): 1/N within each decile portfolio.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>panel: FloatCap-Weight</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weekly R5 portfolio summary from step-04 CNN all_h{k}.xlsx and step-05 benchmark h{k}.xlsx.</t>
+          <t>source sheet='float'; Float market-cap weight at formation (CN: FloatCap / 流通市值).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>panel: TotalCap-Weight</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Return column: Annualized Return (raw portfolio return, annualized). NOT Annualized Active Return.</t>
+          <t>source sheet='total'; Total market-cap weight at formation (CN: TotalCap / 总市值).</t>
         </is>
       </c>
     </row>
@@ -512,7 +512,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sharpe column: Sharpe Ratio = Annualized Return / Annualized Risk (both raw).</t>
+          <t>Weekly R5 portfolio summary from step-04 CNN all_h{k}.xlsx and step-05 benchmark h{k}.xlsx (weekly/). Paper reference: Table I.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H-L: eval horizon H1 (signal at t, return over 1st future rebalance period).</t>
+          <t>Return column: Annualized Return (raw portfolio return, annualized). NOT Annualized Active Return.</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DH Ret2 / DH Ret3: H-L (DH) annualized return at eval horizons H2 / H3 (2nd / 3rd future rebalance period).</t>
+          <t>Sharpe column: Sharpe Ratio = Annualized Return / Annualized Risk (both raw).</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Turnover row: monthly turnover on H-L (DH), paper Table I / GKX (2020) convention (R5 one-week holding ≈ 0.25 month; scaled from backtest Turnover (annualized)).</t>
+          <t>H-L: eval horizon H1 (signal at t, return over 1st future rebalance period).</t>
         </is>
       </c>
     </row>
@@ -559,6 +559,30 @@
         </is>
       </c>
       <c r="B12" t="inlineStr">
+        <is>
+          <t>DH Ret2 / DH Ret3: H-L (DH) annualized return at eval horizons H2 / H3 (2nd / 3rd future rebalance period).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Turnover row: monthly turnover on H-L (DH), paper Table I/II / GKX (2020) convention (holding ≈ 0.25 month(s); scaled from backtest Turnover (annualized)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>H-L and DH Ret2/Ret3 return stars use Newey-West t-stat on the long-short spread.</t>
         </is>
